--- a/CSV元ファイル/Statu.xlsx
+++ b/CSV元ファイル/Statu.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MuscleCat\CSV元ファイル\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{501AA8A2-BBBC-473B-B411-878D7F08B62A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CFEDBB4-785F-4F01-A36D-7772438028A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4635" yWindow="1875" windowWidth="21585" windowHeight="11295" xr2:uid="{CEB2EF47-D34B-411B-B10E-580D0BBFDC1F}"/>
   </bookViews>
@@ -37,18 +37,27 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
-  <si>
-    <t>Speed</t>
-    <phoneticPr fontId="1"/>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>Cat</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>mouse</t>
+    <t>Mouse</t>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>role</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>base_speed</t>
+  </si>
+  <si>
+    <t>speed_growth_per_unit</t>
+  </si>
+  <si>
+    <t>max_speed</t>
   </si>
 </sst>
 </file>
@@ -80,7 +89,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -88,14 +97,186 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -412,22 +593,55 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB3A0544-C170-4E65-9C89-19CD00B8F39A}">
-  <dimension ref="C3:D5"/>
+  <dimension ref="C2:F5"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="4" max="4" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="23" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="3" spans="3:4" x14ac:dyDescent="0.4">
-      <c r="D3" t="s">
+    <row r="2" spans="3:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45"/>
+    <row r="3" spans="3:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="C3" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="3:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="C4" s="10" t="s">
         <v>0</v>
       </c>
+      <c r="D4" s="2">
+        <v>4</v>
+      </c>
+      <c r="E4" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="F4" s="4">
+        <v>5.5</v>
+      </c>
     </row>
-    <row r="4" spans="3:4" x14ac:dyDescent="0.4">
-      <c r="C4" t="s">
+    <row r="5" spans="3:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="C5" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="3:4" x14ac:dyDescent="0.4">
-      <c r="C5" t="s">
-        <v>2</v>
+      <c r="D5" s="5">
+        <v>4.2</v>
+      </c>
+      <c r="E5" s="6">
+        <v>0.05</v>
+      </c>
+      <c r="F5" s="7">
+        <v>4.7</v>
       </c>
     </row>
   </sheetData>
